--- a/docs/thesis/subsurface-heat-mapping-for-geothermal.xlsx
+++ b/docs/thesis/subsurface-heat-mapping-for-geothermal.xlsx
@@ -1041,7 +1041,7 @@
               <color rgb="00808080"/>
               <sz val="10"/>
             </rPr>
-            <t>2026-09-28 11:26 UTC by warehouse/thesis/build.py, run 20260928T110524Z; 21 model calls (claude-sonnet-5), 23 web searches, USD 2.4141, 21.3 minutes. Numbers not found in a cited source are written as not confirmed.</t>
+            <t>2026-09-28 17:04 UTC by warehouse/thesis/build.py, run 20260928T170409Z; 21 model calls (claude-sonnet-5), 23 web searches, USD 2.4141, 0.2 minutes. Numbers not found in a cited source are written as not confirmed.</t>
           </r>
         </is>
       </c>
@@ -2601,7 +2601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J15"/>
+  <dimension ref="B1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2757,42 +2757,42 @@
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>Quaise Energy</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Develops enhanced geothermal systems (EGS) using horizontal drilling and fiber-optic subsurface sensing to site and produce wells for power generation.</t>
+          <t>Millimeter-wave deep-drilling technology aimed at accessing superhot geothermal rock beyond the reach of conventional drilling.</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Co-founded 2017 by CEO Tim Latimer and CTO Jack Norbeck</t>
+          <t>Spun out of the MIT Plasma Science and Fusion Center in 2018; CEO and president Carlos Araque</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>public (NASDAQ: FRVO)</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>$1.89 billion IPO (2026-05-12, 70 million shares at $27/share); prior rounds: $244 million (Feb 2024), $255 million (Dec 2024), $206 million (Jun 2025), $462 million oversubscribed Series E (Dec 2025); $421 million non-recourse project financing for Cape Station (Mar 2026) (not confirmed: 5, 12, 70, 27)</t>
+          <t>$180 million Series B final close (2026-08-27), bringing total funding to $280 million, including a $35 million strategic investment from Nabors Industries; first close of Series B was $134 million (2026-07-07); prior Series A1 of $21 million brought total to over $95 million (2024) (not confirmed: 8, 7, 2024)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Houston, Texas</t>
+          <t>Cambridge, Massachusetts</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>396 MW PPA with Google announced 2026-09-01 for Cape Station in Utah, with an option to expand offtake by approximately 600 MW for a total of nearly 1 GW by June 2030</t>
+          <t>Nabors Industries' investment positions it as Quaise's largest shareholder with a fully diluted ownership of 14%</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>S140, S137, S52, S53, S145, S54, S61, S62</t>
+          <t>S109, S110, S111, S113, S116</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -2804,136 +2804,136 @@
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Quaise Energy</t>
+          <t>Sage Geosystems</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Millimeter-wave deep-drilling technology aimed at accessing superhot geothermal rock beyond the reach of conventional drilling.</t>
+          <t>Develops geopressured geothermal systems, aiming to make geothermal energy accessible at depths economically drillable with existing oilfield technologies and equipment.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Spun out of the MIT Plasma Science and Fusion Center in 2018; CEO and president Carlos Araque</t>
+          <t>Founded 2020 by CEO and co-founder Cindy Taff, President and co-founder Dr. Lev Ring, and CTO and co-founder Lance Cook</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series B (per Pitchbook, not a primary press release found)</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>$180 million Series B final close (2026-08-27), bringing total funding to $280 million, including a $35 million strategic investment from Nabors Industries; first close of Series B was $134 million (2026-07-07); prior Series A1 of $21 million brought total to over $95 million (2024) (not confirmed: 8, 7, 2024)</t>
+          <t>First close of $17 million Series A led by Chesapeake Energy Corporation (2024); has raised $159.0 million across 3 funding rounds, most recently a $97.0 million Series B in January 2026, per Pitchbook (not confirmed: 2024)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Cambridge, Massachusetts</t>
+          <t>Houston, Texas</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Nabors Industries' investment positions it as Quaise's largest shareholder with a fully diluted ownership of 14%</t>
+          <t>Ormat's Q4-2025 filing notes advancing enhanced geothermal systems (EGS) through SLB joint venture and Sage investment and cooperation agreement</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>S109, S110, S111, S113, S116</t>
+          <t>S80, S81, S82, S88, S121</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>100: 3 independent sources, latest 2026; stage confirmed and raised confirmed by a primary source</t>
+          <t>80: 3 independent sources, latest 2026; stage not confirmed and raised not confirmed by a primary source</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Sage Geosystems</t>
+          <t>XGS Energy</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Develops geopressured geothermal systems, aiming to make geothermal energy accessible at depths economically drillable with existing oilfield technologies and equipment.</t>
+          <t>Heat-harvesting geothermal technology that drills a single directional well into rock at 250 degrees C or higher and pulls heat into the well through a network of thermally conductive material.</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Founded 2020 by CEO and co-founder Cindy Taff, President and co-founder Dr. Lev Ring, and CTO and co-founder Lance Cook</t>
+          <t>Led by CEO Josh Prueher, COO Ghazal Izadi and CTO Axel-Pierre Bois</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Series B (per Pitchbook, not a primary press release found)</t>
+          <t>Series A (extended)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>First close of $17 million Series A led by Chesapeake Energy Corporation (2024); has raised $159.0 million across 3 funding rounds, most recently a $97.0 million Series B in January 2026, per Pitchbook (not confirmed: 2024)</t>
+          <t>Has raised $56.7 million across 4 funding rounds: $9.7 million led by Constellation Technology Ventures, $14 million Series A led by Anzu Partners, a $20 million Series A extension led by Valo Ventures and VoLo Earth Ventures (2024-05-21, total Series A of $34.5 million), and $13 million in additional financing (2025-03) (not confirmed: 9.7, 14, 2024, 5)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Houston, Texas</t>
+          <t>Palo Alto, California</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Ormat's Q4-2025 filing notes advancing enhanced geothermal systems (EGS) through SLB joint venture and Sage investment and cooperation agreement</t>
+          <t>Plans a demonstration project in California at a shut-in geothermal well originally drilled in the 1980s</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>S80, S81, S82, S88, S121</t>
+          <t>S99, S100, S101, S104, S107</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>80: 3 independent sources, latest 2026; stage not confirmed and raised not confirmed by a primary source</t>
+          <t>100: 3 independent sources, latest 2025; stage confirmed and raised confirmed by a primary source</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>XGS Energy</t>
+          <t>Bedrock Energy</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Heat-harvesting geothermal technology that drills a single directional well into rock at 250 degrees C or higher and pulls heat into the well through a network of thermally conductive material.</t>
+          <t>Designs geothermal design and installation technology combining autonomous drilling and advanced subsurface modeling, for heating and cooling buildings.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Led by CEO Josh Prueher, COO Ghazal Izadi and CTO Axel-Pierre Bois</t>
+          <t>Co-founded 2022 by CEO Joselyn Lai and CTO Silviu Livescu</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Series A (extended)</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Has raised $56.7 million across 4 funding rounds: $9.7 million led by Constellation Technology Ventures, $14 million Series A led by Anzu Partners, a $20 million Series A extension led by Valo Ventures and VoLo Earth Ventures (2024-05-21, total Series A of $34.5 million), and $13 million in additional financing (2025-03) (not confirmed: 9.7, 14, 2024, 5)</t>
+          <t>$8.5 million seed led by Wireframe Ventures (2023-10-11); $12 million Series A led by Titanium Ventures, with Energy Impact Partners and Sustainable Future Ventures (2025-01) (not confirmed: 10, 2025, 1)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Palo Alto, California</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Plans a demonstration project in California at a shut-in geothermal well originally drilled in the 1980s</t>
+          <t>CEO describes its drilling technology as able to "read the ground while drilling," drilling three to eight times faster than conventional methods</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>S99, S100, S101, S104, S107</t>
+          <t>S89, S90, S91, S92, S93, S95</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -2945,146 +2945,99 @@
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Bedrock Energy</t>
+          <t>Project InnerSpace</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Designs geothermal design and installation technology combining autonomous drilling and advanced subsurface modeling, for heating and cooling buildings.</t>
+          <t>Nonprofit building the Geothermal Exploration Opportunities Map (GeoMap), which combines the work of more than 100 scientists globally to let stakeholders identify the quality and cost to develop geothermal resources beneath them.</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Co-founded 2022 by CEO Joselyn Lai and CTO Silviu Livescu</t>
+          <t>Led by Jamie Beard, with support of Schmidt Futures, the philanthropic initiative founded by Eric and Wendy Schmidt</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>nonprofit (not applicable)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>$8.5 million seed led by Wireframe Ventures (2023-10-11); $12 million Series A led by Titanium Ventures, with Energy Impact Partners and Sustainable Future Ventures (2025-01) (not confirmed: 10, 2025, 1)</t>
+          <t>$16.6 million in research investments to date; an $11.5 million budget with a self-reported $4 million funding gap for the remainder of 2025 (both self-reported by the organization)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>CEO describes its drilling technology as able to "read the ground while drilling," drilling three to eight times faster than conventional methods</t>
+          <t>SLB has partnered with Google Cloud and Project InnerSpace to complement its GeoMap dataset with SLB GeothermEx geothermal consulting services</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>S89, S90, S91, S92, S93, S95</t>
+          <t>S131, S146, S149, S150, S151, S152</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>100: 3 independent sources, latest 2025; stage confirmed and raised confirmed by a primary source</t>
+          <t>80: 3 independent sources, latest 2025; stage not confirmed and raised not confirmed by a primary source</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Project InnerSpace</t>
+          <t>Mantle Reach Power</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Nonprofit building the Geothermal Exploration Opportunities Map (GeoMap), which combines the work of more than 100 scientists globally to let stakeholders identify the quality and cost to develop geothermal resources beneath them.</t>
+          <t>Geothermal developer that entered a commercial agreement with Baker Hughes to accelerate large-scale geothermal energy deployment across North America.</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Led by Jamie Beard, with support of Schmidt Futures, the philanthropic initiative founded by Eric and Wendy Schmidt</t>
+          <t>not disclosed</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>nonprofit (not applicable)</t>
+          <t>not disclosed</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>$16.6 million in research investments to date; an $11.5 million budget with a self-reported $4 million funding gap for the remainder of 2025 (both self-reported by the organization)</t>
+          <t>not disclosed; backed by EnCap Energy Transition Fund III (amount not disclosed)</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>not disclosed</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>SLB has partnered with Google Cloud and Project InnerSpace to complement its GeoMap dataset with SLB GeothermEx geothermal consulting services</t>
+          <t>Baker Hughes entered a commercial agreement with Mantle Reach Power to accelerate large-scale geothermal energy deployment across North America</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>S131, S146, S149, S150, S151, S152</t>
+          <t>S128</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>80: 3 independent sources, latest 2025; stage not confirmed and raised not confirmed by a primary source</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Mantle Reach Power</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Geothermal developer that entered a commercial agreement with Baker Hughes to accelerate large-scale geothermal energy deployment across North America.</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>not disclosed</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>not disclosed</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>not disclosed; backed by EnCap Energy Transition Fund III (amount not disclosed)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>not disclosed</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Baker Hughes entered a commercial agreement with Mantle Reach Power to accelerate large-scale geothermal energy deployment across North America</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>S128</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
           <t>40: 1 independent source, latest 2026; stage not confirmed and raised not confirmed by a primary source</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="360" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="14" ht="300" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3103,7 +3056,7 @@
               <color rgb="00808080"/>
               <sz val="10"/>
             </rPr>
-            <t>S1 Zanskar - Crunchbase Company Profile &amp; Funding; S5 Zanskar Geothermal; S8 Zanskar | Lowercarbon Capital; S21 O’Melveny Advises Zanskar on US$115M Series C Funding - O'Me; S22 Zanskar raises $115M Series C following record-setting year ; S25 Geothermal Startup Zanskar Raises $115 Million to Find and D; S26 Armed with $115 million, geothermal startup Zanskar gets rea; S67 O’Melveny Advises Zanskar on US$30 Million Series B Funding ; S69 Zanskar Raises $30 Million to Accelerate Discovery of Geothe; S73 Zanskar Closes $40M in Novel Development Capital Financing, ; S140 Fervo Energy; S137 Bill Gates-backed geothermal developer Fervo raises $1.89B i; S52 Fervo Energy Geothermal 2026, 400 MW Cape Station PPA - Enki; S53 Fervo Energy Raises $462 Million Series E to Accelerate Geot; S145 Fervo Energy: From Startup to Geothermal Leader - Energy New; S54 Fervo Energy and Google Sign 396 MW PPA - Fervo Energy; S61 Enhanced geothermal notches another win as Google buys 400 M; S62 Fervo Shares Surge on Geothermal Power Deal With Google; S109 Quaise Energy Raises $134M To Build Superhot Geothermal Powe; S110 Quaise Energy Raises $134 Million in Initial Close of Series; S111 Quaise raises $180 million in final close of Series B to fun; S113 Nabors Expands Geothermal Growth Platform with $35 Million S; S116 Quaise Energy | Quaise Energy Raises $21 Million to Accelera; S80 Sage Geosystems Raises $17 Million in Series A, Announces Wo; S81 Clean Energy Startup Sage Geosystems Raises $17 Million for ; S82 SAGE Geosystems: Funding, Team &amp; Investors | Startup Intros; S88 Who Owns Sage Geosystems Company? – businessmodelcanvastempl; S121 Ormat Technologies Inc. - Ormat Technologies Reports Fourth ; S99 Geothermal Innovator XGS Energy Completes Oversubscribed $20; S100 XGS Energy Raises $13 Million to Deploy Geothermal Energy Pr; S101 XGS Energy: Funding, Team &amp; Investors | Startup Intros; S104 XGS Energy Secures $19M in Financing and Adds Industry Leade; S107 Exclusive: XGS raises $20M for geothermal tech; S89 Inside Bedrock Energy’s Plan to Deliver Affordable Geotherma; S90 Bedrock Energy Secures $12M to Expand Geothermal in the Moun; S91 Bedrock Energy secures $12m in funding to scale business; S92 Geothermal Startup Bedrock Energy Secures $12M Series A Rais; S93 Geothermal Tech Startup Bedrock Raises $12 Million to Scale ; S95 Bedrock Energy Raises $8.5M to Decarbonize Commercial Real E; S131 SCHLUMBERGER LIMITED/NV - Form 8-K - FY2025; S146 Project InnerSpace: Top Climate Nonprofit Evaluation | Givin; S149 Project InnerSpace Among Top Five Climate Nonprofits for 202; S150 Project InnerSpace Becomes the Largest Nonprofit Funder of G; S151 Project InnerSpace | LinkedIn; S152 Project InnerSpace's GeoMap; S128 Baker Hughes Unlocks Geothermal Opportunity in North America</t>
+            <t>S1 Zanskar - Crunchbase Company Profile &amp; Funding; S5 Zanskar Geothermal; S8 Zanskar | Lowercarbon Capital; S21 O’Melveny Advises Zanskar on US$115M Series C Funding - O'Me; S22 Zanskar raises $115M Series C following record-setting year ; S25 Geothermal Startup Zanskar Raises $115 Million to Find and D; S26 Armed with $115 million, geothermal startup Zanskar gets rea; S67 O’Melveny Advises Zanskar on US$30 Million Series B Funding ; S69 Zanskar Raises $30 Million to Accelerate Discovery of Geothe; S73 Zanskar Closes $40M in Novel Development Capital Financing, ; S109 Quaise Energy Raises $134M To Build Superhot Geothermal Powe; S110 Quaise Energy Raises $134 Million in Initial Close of Series; S111 Quaise raises $180 million in final close of Series B to fun; S113 Nabors Expands Geothermal Growth Platform with $35 Million S; S116 Quaise Energy | Quaise Energy Raises $21 Million to Accelera; S80 Sage Geosystems Raises $17 Million in Series A, Announces Wo; S81 Clean Energy Startup Sage Geosystems Raises $17 Million for ; S82 SAGE Geosystems: Funding, Team &amp; Investors | Startup Intros; S88 Who Owns Sage Geosystems Company? – businessmodelcanvastempl; S121 Ormat Technologies Inc. - Ormat Technologies Reports Fourth ; S99 Geothermal Innovator XGS Energy Completes Oversubscribed $20; S100 XGS Energy Raises $13 Million to Deploy Geothermal Energy Pr; S101 XGS Energy: Funding, Team &amp; Investors | Startup Intros; S104 XGS Energy Secures $19M in Financing and Adds Industry Leade; S107 Exclusive: XGS raises $20M for geothermal tech; S89 Inside Bedrock Energy’s Plan to Deliver Affordable Geotherma; S90 Bedrock Energy Secures $12M to Expand Geothermal in the Moun; S91 Bedrock Energy secures $12m in funding to scale business; S92 Geothermal Startup Bedrock Energy Secures $12M Series A Rais; S93 Geothermal Tech Startup Bedrock Raises $12 Million to Scale ; S95 Bedrock Energy Raises $8.5M to Decarbonize Commercial Real E; S131 SCHLUMBERGER LIMITED/NV - Form 8-K - FY2025; S146 Project InnerSpace: Top Climate Nonprofit Evaluation | Givin; S149 Project InnerSpace Among Top Five Climate Nonprofits for 202; S150 Project InnerSpace Becomes the Largest Nonprofit Funder of G; S151 Project InnerSpace | LinkedIn; S152 Project InnerSpace's GeoMap; S128 Baker Hughes Unlocks Geothermal Opportunity in North America</t>
           </r>
         </is>
       </c>
@@ -3111,8 +3064,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B14:I14"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3221,11 +3174,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
+      <c r="B7" s="6" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Sage Geosystems</t>
@@ -3248,7 +3197,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>led by Chesapeake Energy Corporation, with Arch Meredith and Helium-3 Ventures</t>
+          <t>Chesapeake Energy Corporation</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -3258,11 +3207,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
+      <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Zanskar</t>
@@ -3283,11 +3228,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>led by Obvious Ventures, with Munich Re Ventures, Union Square Ventures, Lowercarbon Capital, Safar Partners, First Star Ventures and Clearvision Ventures</t>
-        </is>
-      </c>
+      <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
           <t>S67, S26</t>
@@ -3295,11 +3236,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
+      <c r="B9" s="6" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>XGS Energy</t>
@@ -3322,7 +3259,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>led by Valo Ventures and VoLo Earth Ventures</t>
+          <t>Valo Ventures; VoLo Earth Ventures</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -3332,11 +3269,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>2023-10-11</t>
-        </is>
-      </c>
+      <c r="B10" s="7" t="inlineStr"/>
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Bedrock Energy</t>
@@ -3359,7 +3292,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>led by Wireframe Ventures, with Overture Climate VC, Long Journey Ventures, Cantos, Toba Capital, First Star Ventures, Divergent Capital and Climate Capital</t>
+          <t>Wireframe Ventures</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -3369,11 +3302,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
+      <c r="B11" s="6" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Bedrock Energy</t>
@@ -3396,7 +3325,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>led by Titanium Ventures, with Energy Impact Partners and Sustainable Future Ventures</t>
+          <t>Titanium Ventures; Energy Impact Partners; Sustainable Future Ventures</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -3406,11 +3335,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="inlineStr"/>
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>XGS Energy</t>
@@ -3443,11 +3368,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Quaise Energy</t>
@@ -3468,11 +3389,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>led by Prelude Ventures and Safar Partners</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr">
         <is>
           <t>S116</t>
@@ -3480,11 +3397,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
+      <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Zanskar</t>
@@ -3507,7 +3420,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>led by Spring Lane Capital, with Obvious Ventures, Union Square Ventures and Lowercarbon Capital</t>
+          <t>Spring Lane Capital; Obvious Ventures; Union Square Ventures; Lowercarbon Capital</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -3517,11 +3430,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="B15" s="6" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Zanskar</t>
@@ -3542,11 +3451,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>co-led by Just Climate and Spring Lane Capital, with Tierra Adentro Growth Capital</t>
-        </is>
-      </c>
+      <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
           <t>S73</t>
@@ -3665,11 +3570,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
+      <c r="B19" s="6" t="inlineStr"/>
       <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Fervo Energy</t>
@@ -3727,11 +3628,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>led by B Capital</t>
-        </is>
-      </c>
+      <c r="G20" s="7" t="inlineStr"/>
       <c r="H20" s="7" t="inlineStr">
         <is>
           <t>S53, S137</t>
@@ -3776,11 +3673,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+      <c r="B22" s="7" t="inlineStr"/>
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Fervo Energy</t>
@@ -3803,7 +3696,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>not disclosed (public offering, 70 million shares at $27/share)</t>
+          <t>not disclosed</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -3813,11 +3706,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
+      <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Quaise Energy</t>
@@ -3840,7 +3729,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>led by Prelude Ventures, with strategic investments from JERA and Idemitsu</t>
+          <t>Prelude Ventures; Idemitsu</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -3875,11 +3764,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>led by Prelude Ventures, with a $35 million strategic investment from Nabors Industries</t>
-        </is>
-      </c>
+      <c r="G24" s="7" t="inlineStr"/>
       <c r="H24" s="7" t="inlineStr">
         <is>
           <t>S111, S113</t>
@@ -3927,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I15"/>
+  <dimension ref="B1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4319,8 +4204,41 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="75" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Fervo Energy</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>public company (from Landscape)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>NASDAQ: FRVO</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>not disclosed</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>S140, S137, S52, S53, S145, S54, S61, S62</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="105" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4339,7 +4257,7 @@
               <color rgb="00808080"/>
               <sz val="10"/>
             </rPr>
-            <t>S121 Ormat Technologies Inc. - Ormat Technologies Reports Fourth ; S119 ANNUAL REPORT 2024; S131 SCHLUMBERGER LIMITED/NV - Form 8-K - FY2025; S128 Baker Hughes Unlocks Geothermal Opportunity in North America; S113 Nabors Expands Geothermal Growth Platform with $35 Million S; S111 Quaise raises $180 million in final close of Series B to fun; S54 Fervo Energy and Google Sign 396 MW PPA - Fervo Energy; S61 Enhanced geothermal notches another win as Google buys 400 M; S62 Fervo Shares Surge on Geothermal Power Deal With Google</t>
+            <t>S121 Ormat Technologies Inc. - Ormat Technologies Reports Fourth ; S119 ANNUAL REPORT 2024; S131 SCHLUMBERGER LIMITED/NV - Form 8-K - FY2025; S128 Baker Hughes Unlocks Geothermal Opportunity in North America; S113 Nabors Expands Geothermal Growth Platform with $35 Million S; S111 Quaise raises $180 million in final close of Series B to fun; S54 Fervo Energy and Google Sign 396 MW PPA - Fervo Energy; S61 Enhanced geothermal notches another win as Google buys 400 M; S62 Fervo Shares Surge on Geothermal Power Deal With Google; S140 Fervo Energy; S137 Bill Gates-backed geothermal developer Fervo raises $1.89B i; S52 Fervo Energy Geothermal 2026, 400 MW Cape Station PPA - Enki; S53 Fervo Energy Raises $462 Million Series E to Accelerate Geot; S145 Fervo Energy: From Startup to Geothermal Leader - Energy New</t>
           </r>
         </is>
       </c>
@@ -4347,8 +4265,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B16:I16"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5510,7 +5428,7 @@
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>'Scope'!B6; 'Landscape'!B7:J7; 'Landscape'!B15</t>
+          <t>'Scope'!B6; 'Landscape'!B7:J7; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5552,7 @@
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B7:J7; 'Landscape'!B15</t>
+          <t>'Landscape'!B7:J7; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5648,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>'Scope'!B6; 'Scope'!B10:C10; 'Scope'!B15; 'Fundamentals'!B17:F17; 'Fundamentals'!B29; 'Landscape'!B7:J7; 'Landscape'!B15; 'Risks'!B12</t>
+          <t>'Scope'!B6; 'Scope'!B10:C10; 'Scope'!B15; 'Fundamentals'!B17:F17; 'Fundamentals'!B29; 'Landscape'!B7:J7; 'Landscape'!B14; 'Risks'!B12</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6028,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>'Fundamentals'!B19:F19; 'Fundamentals'!B21:F21; 'Fundamentals'!B29; 'Trends'!B126:E126; 'Trends'!B127:E127; 'Trends'!B128:E128; 'Trends'!B129:E129; 'Trends'!B130; 'Landscape'!B7:J7; 'Landscape'!B15; 'Capital'!B14:H14; 'Capital'!B25</t>
+          <t>'Fundamentals'!B19:F19; 'Fundamentals'!B21:F21; 'Fundamentals'!B29; 'Trends'!B126:E126; 'Trends'!B127:E127; 'Trends'!B128:E128; 'Trends'!B129:E129; 'Trends'!B130; 'Landscape'!B7:J7; 'Landscape'!B14; 'Capital'!B14:H14; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6060,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>'Fundamentals'!B18:F18; 'Fundamentals'!B21:F21; 'Fundamentals'!B29; 'Trends'!B126:E126; 'Trends'!B127:E127; 'Trends'!B128:E128; 'Trends'!B129:E129; 'Trends'!B130; 'Landscape'!B7:J7; 'Landscape'!B15; 'Capital'!B14:H14; 'Capital'!B25</t>
+          <t>'Fundamentals'!B18:F18; 'Fundamentals'!B21:F21; 'Fundamentals'!B29; 'Trends'!B126:E126; 'Trends'!B127:E127; 'Trends'!B128:E128; 'Trends'!B129:E129; 'Trends'!B130; 'Landscape'!B7:J7; 'Landscape'!B14; 'Capital'!B14:H14; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6156,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B7:J7; 'Landscape'!B15; 'Capital'!B14:H14; 'Capital'!B25</t>
+          <t>'Landscape'!B7:J7; 'Landscape'!B14; 'Capital'!B14:H14; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6188,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B7:J7; 'Landscape'!B15; 'Capital'!B8:H8; 'Capital'!B25</t>
+          <t>'Landscape'!B7:J7; 'Landscape'!B14; 'Capital'!B8:H8; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -7046,7 +6964,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>'Fundamentals'!B22:F22; 'Fundamentals'!B23:F23; 'Fundamentals'!B25:F25; 'Fundamentals'!B29; 'Landscape'!B8:J8; 'Landscape'!B15; 'Capital'!B21:H21; 'Capital'!B22:H22; 'Capital'!B25</t>
+          <t>'Fundamentals'!B22:F22; 'Fundamentals'!B23:F23; 'Fundamentals'!B25:F25; 'Fundamentals'!B29; 'Capital'!B21:H21; 'Capital'!B22:H22; 'Capital'!B25; 'Incumbents'!B15:H15; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -7078,7 +6996,7 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>'Fundamentals'!B24:F24; 'Fundamentals'!B25:F25; 'Fundamentals'!B29; 'Landscape'!B8:J8; 'Landscape'!B15; 'Capital'!B20:H20; 'Capital'!B25</t>
+          <t>'Fundamentals'!B24:F24; 'Fundamentals'!B25:F25; 'Fundamentals'!B29; 'Capital'!B20:H20; 'Capital'!B25; 'Incumbents'!B15:H15; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7028,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>'Scope'!B14:C14; 'Scope'!B15; 'Fundamentals'!B26:F26; 'Fundamentals'!B29; 'Landscape'!B8:J8; 'Landscape'!B15; 'Incumbents'!B13:H13; 'Incumbents'!B14:H14; 'Incumbents'!B15</t>
+          <t>'Scope'!B14:C14; 'Scope'!B15; 'Fundamentals'!B26:F26; 'Fundamentals'!B29; 'Incumbents'!B13:H13; 'Incumbents'!B14:H14; 'Incumbents'!B15:H15; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7248,7 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B8:J8; 'Landscape'!B15; 'Incumbents'!B13:H13; 'Incumbents'!B15</t>
+          <t>'Incumbents'!B13:H13; 'Incumbents'!B15:H15; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7280,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B8:J8; 'Landscape'!B15; 'Incumbents'!B14:H14; 'Incumbents'!B15</t>
+          <t>'Incumbents'!B14:H14; 'Incumbents'!B15:H15; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7428,7 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>'Fundamentals'!B20:F20; 'Fundamentals'!B21:F21; 'Fundamentals'!B29; 'Trends'!B126:E126; 'Trends'!B127:E127; 'Trends'!B128:E128; 'Trends'!B129:E129; 'Trends'!B130; 'Landscape'!B7:J7; 'Landscape'!B15; 'Capital'!B8:H8; 'Capital'!B25</t>
+          <t>'Fundamentals'!B20:F20; 'Fundamentals'!B21:F21; 'Fundamentals'!B29; 'Trends'!B126:E126; 'Trends'!B127:E127; 'Trends'!B128:E128; 'Trends'!B129:E129; 'Trends'!B130; 'Landscape'!B7:J7; 'Landscape'!B14; 'Capital'!B8:H8; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7492,7 @@
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B7:J7; 'Landscape'!B15</t>
+          <t>'Landscape'!B7:J7; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7616,7 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>'Trends'!B126:E126; 'Trends'!B127:E127; 'Trends'!B128:E128; 'Trends'!B129:E129; 'Trends'!B130; 'Landscape'!B7:J7; 'Landscape'!B15; 'Capital'!B15:H15; 'Capital'!B25</t>
+          <t>'Trends'!B126:E126; 'Trends'!B127:E127; 'Trends'!B128:E128; 'Trends'!B129:E129; 'Trends'!B130; 'Landscape'!B7:J7; 'Landscape'!B14; 'Capital'!B15:H15; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7824,7 @@
       <c r="F85" s="7" t="inlineStr"/>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B10:J10; 'Landscape'!B15; 'Capital'!B7:H7; 'Capital'!B25</t>
+          <t>'Landscape'!B9:J9; 'Landscape'!B14; 'Capital'!B7:H7; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7856,7 @@
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B10:J10; 'Landscape'!B15</t>
+          <t>'Landscape'!B9:J9; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7888,7 @@
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B10:J10; 'Landscape'!B15; 'Capital'!B16:H16; 'Capital'!B25</t>
+          <t>'Landscape'!B9:J9; 'Landscape'!B14; 'Capital'!B16:H16; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8072,7 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B10:J10; 'Landscape'!B15</t>
+          <t>'Landscape'!B9:J9; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8104,7 @@
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B12:J12; 'Landscape'!B15; 'Capital'!B11:H11; 'Capital'!B25</t>
+          <t>'Landscape'!B11:J11; 'Landscape'!B14; 'Capital'!B11:H11; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8136,7 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B12:J12; 'Landscape'!B15</t>
+          <t>'Landscape'!B11:J11; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8168,7 @@
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B12:J12; 'Landscape'!B15</t>
+          <t>'Landscape'!B11:J11; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8200,7 @@
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B12:J12; 'Landscape'!B15</t>
+          <t>'Landscape'!B11:J11; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8232,7 @@
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B12:J12; 'Landscape'!B15</t>
+          <t>'Landscape'!B11:J11; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8288,7 @@
       <c r="F100" s="6" t="inlineStr"/>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B12:J12; 'Landscape'!B15; 'Capital'!B10:H10; 'Capital'!B25</t>
+          <t>'Landscape'!B11:J11; 'Landscape'!B14; 'Capital'!B10:H10; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8412,7 @@
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B11:J11; 'Landscape'!B15; 'Capital'!B9:H9; 'Capital'!B25</t>
+          <t>'Landscape'!B10:J10; 'Landscape'!B14; 'Capital'!B9:H9; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8444,7 @@
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B11:J11; 'Landscape'!B15; 'Capital'!B12:H12; 'Capital'!B25</t>
+          <t>'Landscape'!B10:J10; 'Landscape'!B14; 'Capital'!B12:H12; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8476,7 @@
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B11:J11; 'Landscape'!B15</t>
+          <t>'Landscape'!B10:J10; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8564,7 @@
       <c r="F109" s="7" t="inlineStr"/>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B11:J11; 'Landscape'!B15</t>
+          <t>'Landscape'!B10:J10; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8648,7 @@
       <c r="F112" s="6" t="inlineStr"/>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B11:J11; 'Landscape'!B15; 'Capital'!B9:H9; 'Capital'!B25</t>
+          <t>'Landscape'!B10:J10; 'Landscape'!B14; 'Capital'!B9:H9; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8712,7 @@
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B9:J9; 'Landscape'!B15; 'Capital'!B23:H23; 'Capital'!B25</t>
+          <t>'Landscape'!B8:J8; 'Landscape'!B14; 'Capital'!B23:H23; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8744,7 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B9:J9; 'Landscape'!B15; 'Capital'!B23:H23; 'Capital'!B25</t>
+          <t>'Landscape'!B8:J8; 'Landscape'!B14; 'Capital'!B23:H23; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8776,7 @@
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B9:J9; 'Landscape'!B15; 'Capital'!B24:H24; 'Capital'!B25; 'Incumbents'!B12:H12; 'Incumbents'!B15</t>
+          <t>'Landscape'!B8:J8; 'Landscape'!B14; 'Capital'!B24:H24; 'Capital'!B25; 'Incumbents'!B12:H12; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8836,7 @@
       <c r="F118" s="6" t="inlineStr"/>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B9:J9; 'Landscape'!B15; 'Capital'!B24:H24; 'Capital'!B25; 'Incumbents'!B11:H11; 'Incumbents'!B12:H12; 'Incumbents'!B15</t>
+          <t>'Landscape'!B8:J8; 'Landscape'!B14; 'Capital'!B24:H24; 'Capital'!B25; 'Incumbents'!B11:H11; 'Incumbents'!B12:H12; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -9014,7 +8932,7 @@
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B9:J9; 'Landscape'!B15; 'Capital'!B13:H13; 'Capital'!B25</t>
+          <t>'Landscape'!B8:J8; 'Landscape'!B14; 'Capital'!B13:H13; 'Capital'!B25</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9024,7 @@
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>'Incumbents'!B8:H8; 'Incumbents'!B15</t>
+          <t>'Incumbents'!B8:H8; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9084,7 @@
       <c r="F126" s="6" t="inlineStr"/>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B10:J10; 'Landscape'!B15; 'Incumbents'!B7:H7; 'Incumbents'!B15</t>
+          <t>'Landscape'!B9:J9; 'Landscape'!B14; 'Incumbents'!B7:H7; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9292,7 @@
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B14:J14; 'Landscape'!B15; 'Incumbents'!B10:H10; 'Incumbents'!B15</t>
+          <t>'Landscape'!B13:J13; 'Landscape'!B14; 'Incumbents'!B10:H10; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9380,7 @@
       <c r="F136" s="6" t="inlineStr"/>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B13:J13; 'Landscape'!B15; 'Incumbents'!B9:H9; 'Incumbents'!B15</t>
+          <t>'Landscape'!B12:J12; 'Landscape'!B14; 'Incumbents'!B9:H9; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9560,7 @@
       </c>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B8:J8; 'Landscape'!B15; 'Capital'!B17:H17; 'Capital'!B18:H18; 'Capital'!B19:H19; 'Capital'!B20:H20; 'Capital'!B22:H22; 'Capital'!B25</t>
+          <t>'Capital'!B17:H17; 'Capital'!B18:H18; 'Capital'!B19:H19; 'Capital'!B20:H20; 'Capital'!B22:H22; 'Capital'!B25; 'Incumbents'!B15:H15; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9648,7 @@
       <c r="F145" s="7" t="inlineStr"/>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B8:J8; 'Landscape'!B15</t>
+          <t>'Incumbents'!B15:H15; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9804,7 @@
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B8:J8; 'Landscape'!B15; 'Capital'!B21:H21; 'Capital'!B25</t>
+          <t>'Capital'!B21:H21; 'Capital'!B25; 'Incumbents'!B15:H15; 'Incumbents'!B16</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9832,7 @@
       <c r="F151" s="7" t="inlineStr"/>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B13:J13; 'Landscape'!B15</t>
+          <t>'Landscape'!B12:J12; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -10006,7 +9924,7 @@
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B13:J13; 'Landscape'!B15</t>
+          <t>'Landscape'!B12:J12; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -10038,7 +9956,7 @@
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B13:J13; 'Landscape'!B15</t>
+          <t>'Landscape'!B12:J12; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -10070,7 +9988,7 @@
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>'Landscape'!B13:J13; 'Landscape'!B15</t>
+          <t>'Landscape'!B12:J12; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10016,7 @@
       <c r="F157" s="7" t="inlineStr"/>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>'Landscape'!B13:J13; 'Landscape'!B15</t>
+          <t>'Landscape'!B12:J12; 'Landscape'!B14</t>
         </is>
       </c>
     </row>
